--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_24-04-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_24-04-2026.xlsx
@@ -533,17 +533,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£13.00</t>
+          <t>£14.50</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£13.00</t>
+          <t>£14.50</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£13.00</t>
+          <t>£14.50</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -625,17 +625,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£14.06</t>
+          <t>£17.00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£14.06</t>
+          <t>£17.00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£14.06</t>
+          <t>£17.00</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -717,17 +717,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£18.33</t>
+          <t>£21.15</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£18.33</t>
+          <t>£21.15</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>£18.33</t>
+          <t>£21.15</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -809,17 +809,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£18.44</t>
+          <t>£21.90</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£18.44</t>
+          <t>£21.90</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£18.44</t>
+          <t>£21.90</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -901,17 +901,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£23.65</t>
+          <t>£28.00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£23.65</t>
+          <t>£28.00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£23.65</t>
+          <t>£28.00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£26.51</t>
+          <t>£31.00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>£26.51</t>
+          <t>£31.00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>£26.51</t>
+          <t>£31.00</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1085,17 +1085,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£26.50</t>
+          <t>£31.00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£26.50</t>
+          <t>£31.00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£26.50</t>
+          <t>£31.00</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1177,17 +1177,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£29.74</t>
+          <t>£34.50</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£29.74</t>
+          <t>£34.50</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£29.74</t>
+          <t>£34.50</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1269,17 +1269,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£32.52</t>
+          <t>£37.75</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£32.52</t>
+          <t>£37.75</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£32.52</t>
+          <t>£37.75</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£32.50</t>
+          <t>£36.95</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£32.50</t>
+          <t>£36.95</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£32.50</t>
+          <t>£36.95</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1453,17 +1453,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>£38.76</t>
+          <t>£47.40</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>£38.76</t>
+          <t>£47.40</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>£38.76</t>
+          <t>£47.40</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1545,17 +1545,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£40.15</t>
+          <t>£47.32</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£40.15</t>
+          <t>£47.32</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£40.15</t>
+          <t>£47.32</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£47.85</t>
+          <t>£57.20</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£47.85</t>
+          <t>£57.20</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>£47.85</t>
+          <t>£57.20</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: 504 Server Error: Gateway Timeout for url: https://www.planetinsulation.co.uk/products/celotex-pir-tb-ga-xr?variant=42844828631277</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£49.00</t>
+          <t>£57.23</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£49.00</t>
+          <t>£57.23</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1821,17 +1821,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£48.52</t>
+          <t>£56.28</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£48.52</t>
+          <t>£56.28</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£48.52</t>
+          <t>£56.28</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>£60.42</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1913,17 +1913,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>£879.87</t>
+          <t>£995.00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>£879.87</t>
+          <t>£995.00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>£879.87</t>
+          <t>£995.00</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2005,17 +2005,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>£1,129.70</t>
+          <t>£1,295.00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>£1,129.70</t>
+          <t>£1,295.00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>£1,129.70</t>
+          <t>£1,295.00</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>£33.21</t>
+          <t>£40.40</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>£33.21</t>
+          <t>£40.40</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>£33.21</t>
+          <t>£40.40</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2189,17 +2189,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>£40.14</t>
+          <t>£50.00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>£40.14</t>
+          <t>£50.00</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>£40.14</t>
+          <t>£50.00</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>£44.41</t>
+          <t>£53.22</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>£44.41</t>
+          <t>£53.22</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>£44.41</t>
+          <t>£53.22</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2373,17 +2373,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>£50.09</t>
+          <t>£61.00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>£50.09</t>
+          <t>£61.00</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>£50.09</t>
+          <t>£61.00</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2465,17 +2465,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>£53.35</t>
+          <t>£62.85</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>£53.35</t>
+          <t>£62.85</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>£53.35</t>
+          <t>£62.85</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2557,17 +2557,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>£51.69</t>
+          <t>£62.85</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>£51.69</t>
+          <t>£62.85</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>£51.69</t>
+          <t>£62.85</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2649,17 +2649,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>£1,092.60</t>
+          <t>£1,320.00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>£1,092.60</t>
+          <t>£1,320.00</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>£1,092.60</t>
+          <t>£1,320.00</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2741,17 +2741,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
+          <t>£62.50</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
+          <t>£62.50</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>£49.82</t>
+          <t>£62.50</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2833,17 +2833,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>£1,375.00</t>
+          <t>£1,616.00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>£1,375.00</t>
+          <t>£1,616.00</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>£1,375.00</t>
+          <t>£1,616.00</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2925,17 +2925,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>£1,534.00</t>
+          <t>£1,725.00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>£1,534.00</t>
+          <t>£1,725.00</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>£1,534.00</t>
+          <t>£1,725.00</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3017,17 +3017,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>£1,465.00</t>
+          <t>£1,725.00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>£1,465.00</t>
+          <t>£1,725.00</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>£1,465.00</t>
+          <t>£1,725.00</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">

--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_24-04-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_24-04-2026.xlsx
@@ -558,7 +558,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>£13.55</t>
+          <t>£14.91</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>£15.93</t>
+          <t>£17.52</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>£19.65</t>
+          <t>£21.62</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>£20.93</t>
+          <t>£23.02</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>£25.98</t>
+          <t>£28.58</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>£29.08</t>
+          <t>£31.99</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>£29.08</t>
+          <t>£31.99</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>£33.12</t>
+          <t>£36.43</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>£36.23</t>
+          <t>£39.85</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>£35.25</t>
+          <t>£38.78</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>£43.30</t>
+          <t>£47.63</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>£52.10</t>
+          <t>£57.31</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Error: 504 Server Error: Gateway Timeout for url: https://www.planetinsulation.co.uk/products/celotex-pir-tb-ga-xr?variant=42844828631277</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1754,12 +1754,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>£52.88</t>
+          <t>£58.17</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>£65.57</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>£53.35</t>
+          <t>£58.69</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£60.42</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>£983.94</t>
+          <t>£1,082.33</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>£1,235.22</t>
+          <t>£1,358.74</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>£37.77</t>
+          <t>£41.55</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>£46.00</t>
+          <t>£50.60</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>£40.47</t>
+          <t>£44.99</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>£50.51</t>
+          <t>£55.56</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2398,12 +2398,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>£58.91</t>
+          <t>£64.80</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>£76.25</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>£62.78</t>
+          <t>£69.06</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>£67.79</t>
+          <t>£74.57</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>£62.05</t>
+          <t>£68.26</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>£1584.96</t>
+          <t>£1743.52</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>£1764.8</t>
+          <t>£1941.28</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>£1687.52</t>
+          <t>£1856.32</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
